--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484275_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484275_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1724</v>
+        <v>6.7672</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0954</v>
+        <v>7.349</v>
       </c>
       <c r="F2" t="n">
-        <v>2.077</v>
+        <v>-0.5819</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5795</v>
+        <v>3.9489</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0136</v>
+        <v>0.5091</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5659</v>
+        <v>3.4398</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0504</v>
+        <v>7.2159</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8885</v>
+        <v>1.6168</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1619</v>
+        <v>5.5991</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5292</v>
+        <v>-3.267</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1251</v>
+        <v>-1.1077</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4041</v>
+        <v>-2.1593</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5343</v>
+        <v>1.1384</v>
       </c>
       <c r="T2" t="n">
-        <v>0.432</v>
+        <v>0.7973</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1023</v>
+        <v>0.341</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3869</v>
+        <v>-0.6642</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8436</v>
+        <v>5.9235</v>
       </c>
       <c r="E3" t="n">
-        <v>7.407</v>
+        <v>3.7921</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5635</v>
+        <v>2.1314</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9728</v>
+        <v>4.5795</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5024</v>
+        <v>4.0136</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4704</v>
+        <v>0.5659</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3647</v>
+        <v>4.0504</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9263</v>
+        <v>3.8885</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4384</v>
+        <v>0.1619</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3919</v>
+        <v>0.5292</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4239</v>
+        <v>0.1251</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.968</v>
+        <v>0.4041</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3749</v>
+        <v>0.2854</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7185</v>
+        <v>0.1287</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6564</v>
+        <v>0.1567</v>
       </c>
       <c r="V3" t="n">
         <v>0.2772</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2772</v>
+        <v>-0.3869</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0653</v>
+        <v>4.5157</v>
       </c>
       <c r="E4" t="n">
-        <v>5.974</v>
+        <v>6.052</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9087</v>
+        <v>-1.5362</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9489</v>
+        <v>2.9728</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5091</v>
+        <v>1.5024</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4398</v>
+        <v>1.4704</v>
       </c>
       <c r="J4" t="n">
-        <v>7.2159</v>
+        <v>6.3647</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6168</v>
+        <v>1.9263</v>
       </c>
       <c r="L4" t="n">
-        <v>5.5991</v>
+        <v>4.4384</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.267</v>
+        <v>-3.3919</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1077</v>
+        <v>-0.4239</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1593</v>
+        <v>-2.968</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3441</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5635</v>
+        <v>2.047</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5777</v>
+        <v>1.3634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0142</v>
+        <v>0.6836</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4415</v>
+        <v>2.9996</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0333</v>
+        <v>4.3172</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5919</v>
+        <v>-1.3176</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8303</v>
+        <v>1.5816</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0297</v>
+        <v>-0.1036</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.86</v>
+        <v>1.6852</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1707</v>
+        <v>4.239</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9279</v>
+        <v>0.7994</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2428</v>
+        <v>3.4396</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.001</v>
+        <v>-2.6575</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8982</v>
+        <v>-0.903</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.1028</v>
+        <v>-1.7544</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8113</v>
+        <v>0.9808</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5742</v>
+        <v>0.2037</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2371</v>
+        <v>0.7771</v>
       </c>
       <c r="V5" t="n">
         <v>1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3208</v>
+        <v>2.8471</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4478</v>
+        <v>2.686</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.127</v>
+        <v>0.1611</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5816</v>
+        <v>-0.0333</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1036</v>
+        <v>2.8386</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6852</v>
+        <v>-2.8719</v>
       </c>
       <c r="J6" t="n">
-        <v>4.239</v>
+        <v>2.0106</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7994</v>
+        <v>2.7232</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4396</v>
+        <v>-0.7126</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6575</v>
+        <v>-2.0439</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.903</v>
+        <v>0.1154</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7544</v>
+        <v>-2.1593</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>0.302</v>
+        <v>0.8804</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6657</v>
+        <v>0.4335</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9677</v>
+        <v>0.4469</v>
       </c>
       <c r="V6" t="n">
         <v>1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3609</v>
+        <v>1.1892</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5538</v>
+        <v>1.0248</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1929</v>
+        <v>0.1644</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0333</v>
+        <v>-0.2778</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8386</v>
+        <v>1.4351</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8719</v>
+        <v>-1.713</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0106</v>
+        <v>1.3563</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7232</v>
+        <v>1.3149</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7126</v>
+        <v>0.0415</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0439</v>
+        <v>-1.6342</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1154</v>
+        <v>0.1203</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1593</v>
+        <v>-1.7544</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6059</v>
+        <v>1.7443</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6987</v>
+        <v>1.0126</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0929</v>
+        <v>0.7317</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1287</v>
+        <v>0.8595</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9643</v>
+        <v>1.7874</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1644</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2778</v>
+        <v>0.3888</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4351</v>
+        <v>0.241</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.713</v>
+        <v>0.1478</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3563</v>
+        <v>2.9619</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3149</v>
+        <v>0.2507</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>2.7112</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6342</v>
+        <v>-2.5731</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1203</v>
+        <v>-0.0097</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7544</v>
+        <v>-2.5634</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6838</v>
+        <v>1.3303</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.4664</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7317</v>
+        <v>0.8638</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9781</v>
+        <v>0.6353</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5247</v>
+        <v>3.1727</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5466</v>
+        <v>-2.5374</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3888</v>
+        <v>-0.8303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.241</v>
+        <v>2.0297</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1478</v>
+        <v>-2.86</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9619</v>
+        <v>3.1707</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2507</v>
+        <v>2.9279</v>
       </c>
       <c r="L9" t="n">
-        <v>2.7112</v>
+        <v>0.2428</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5731</v>
+        <v>-4.001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0097</v>
+        <v>-0.8982</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.5634</v>
+        <v>-3.1028</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4488</v>
+        <v>2.0051</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2037</v>
+        <v>1.7135</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2451</v>
+        <v>0.2916</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1077</v>
+        <v>-1.4557</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6796</v>
+        <v>-3.6191</v>
       </c>
       <c r="F10" t="n">
-        <v>2.572</v>
+        <v>2.1634</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8386</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5709</v>
+        <v>1.2229</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1432</v>
+        <v>0.2037</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4277</v>
+        <v>1.0192</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2718</v>
+        <v>-3.7445</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8129</v>
+        <v>-3.4491</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4589</v>
+        <v>-0.2955</v>
       </c>
       <c r="G11" t="n">
         <v>-3.283</v>
@@ -1312,13 +1312,13 @@
         <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2074</v>
+        <v>0.3198</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3026</v>
+        <v>0.0613</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.2586</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>19.9318</v>
+        <v>20.5369</v>
       </c>
       <c r="E12" t="n">
-        <v>22.5078</v>
+        <v>23.113</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.576099999999999</v>
+        <v>-2.5762</v>
       </c>
       <c r="G12" t="n">
-        <v>8.208600000000001</v>
+        <v>8.208600000000002</v>
       </c>
       <c r="H12" t="n">
         <v>9.5588</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3501</v>
+        <v>-1.350100000000001</v>
       </c>
       <c r="J12" t="n">
         <v>27.9433</v>
@@ -1390,13 +1390,13 @@
         <v>12.6974</v>
       </c>
       <c r="S12" t="n">
-        <v>11.3492</v>
+        <v>11.9544</v>
       </c>
       <c r="T12" t="n">
-        <v>5.779000000000001</v>
+        <v>6.384099999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>5.5703</v>
+        <v>5.570200000000001</v>
       </c>
       <c r="V12" t="n">
         <v>2.327399999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7579</v>
+        <v>4.5307</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2731</v>
+        <v>6.4753</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5152</v>
+        <v>-1.9446</v>
       </c>
       <c r="G13" t="n">
         <v>3.9283</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5378</v>
+        <v>-1.765</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1362</v>
+        <v>-0.9339</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4016</v>
+        <v>-0.831</v>
       </c>
       <c r="V13" t="n">
         <v>0.6093</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8146</v>
+        <v>3.6133</v>
       </c>
       <c r="E14" t="n">
-        <v>6.886</v>
+        <v>7.0883</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.0714</v>
+        <v>-3.475</v>
       </c>
       <c r="G14" t="n">
         <v>8.462199999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.8663</v>
+        <v>-2.0676</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2902</v>
+        <v>-1.0879</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5761</v>
+        <v>-0.9796</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2186</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9905</v>
+        <v>-0.7338</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5641</v>
+        <v>0.7663</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5546</v>
+        <v>-1.5001</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0639</v>
@@ -1624,13 +1624,13 @@
         <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5359</v>
+        <v>-0.2792</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3631</v>
+        <v>-0.1609</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1728</v>
+        <v>-0.1183</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.19</v>
+        <v>-1.2768</v>
       </c>
       <c r="E16" t="n">
-        <v>0.914</v>
+        <v>0.6107</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1041</v>
+        <v>-1.8875</v>
       </c>
       <c r="G16" t="n">
         <v>-1.9599</v>
@@ -1702,13 +1702,13 @@
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4022</v>
+        <v>-0.489</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1569</v>
+        <v>-0.1464</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5591</v>
+        <v>-0.3426</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0214</v>
+        <v>-1.8697</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9973</v>
+        <v>-0.3546</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0187</v>
+        <v>-1.5151</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6493</v>
+        <v>-1.6254</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9355</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7138</v>
+        <v>-0.7418</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9519</v>
+        <v>1.0313</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1023</v>
+        <v>0.2891</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8496</v>
+        <v>0.7422</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.6012</v>
+        <v>-2.6567</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0379</v>
+        <v>-1.1727</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5634</v>
+        <v>-1.484</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4623</v>
+        <v>-0.4945</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9546</v>
+        <v>-0.4092</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4923</v>
+        <v>-0.0854</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8865</v>
+        <v>0.0549</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8865</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2276</v>
+        <v>-2.1266</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.658</v>
+        <v>1.3007</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5696</v>
+        <v>-3.4273</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6254</v>
+        <v>-1.6493</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.9355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7418</v>
+        <v>-0.7138</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0313</v>
+        <v>1.9519</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2891</v>
+        <v>0.1023</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7422</v>
+        <v>1.8496</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6567</v>
+        <v>-3.6012</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1727</v>
+        <v>-1.0379</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.484</v>
+        <v>-2.5634</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.5675</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7125</v>
+        <v>-0.6512</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1398</v>
+        <v>0.0838</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0549</v>
+        <v>-0.8865</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0549</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7114</v>
+        <v>-4.0258</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4549</v>
+        <v>-3.7265</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2565</v>
+        <v>-0.2993</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.4359</v>
+        <v>-3.6625</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.9786</v>
+        <v>-2.0573</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4574</v>
+        <v>-1.6052</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9695</v>
+        <v>-1.6751</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.9407</v>
+        <v>-0.6102</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9712</v>
+        <v>-1.0649</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4664</v>
+        <v>-1.9874</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0379</v>
+        <v>-1.4472</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4285</v>
+        <v>-0.5403</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0837</v>
+        <v>-1.2498</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5147</v>
+        <v>-0.5976</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.431</v>
+        <v>-0.6522</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6642</v>
+        <v>0.8865</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.4996</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1254</v>
+        <v>-4.2952</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4859</v>
+        <v>-3.7893</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6394</v>
+        <v>-0.506</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5557</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6163</v>
+        <v>-0.7862</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1457</v>
+        <v>-0.449</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4706</v>
+        <v>-0.3372</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2331</v>
+        <v>-4.5475</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8276</v>
+        <v>-2.2638</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4055</v>
+        <v>-2.2837</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6625</v>
+        <v>-5.4359</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0573</v>
+        <v>-3.9786</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6052</v>
+        <v>-1.4574</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6751</v>
+        <v>-1.9695</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6102</v>
+        <v>-2.9407</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0649</v>
+        <v>0.9712</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9874</v>
+        <v>-3.4664</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4472</v>
+        <v>-1.0379</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5403</v>
+        <v>-2.4285</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4571</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6987</v>
+        <v>-0.2943</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7584</v>
+        <v>-0.4582</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8865</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3869</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.005000000000001</v>
+        <v>-7.8521</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6321</v>
+        <v>-3.531</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3729</v>
+        <v>-4.3211</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6465</v>
@@ -2170,13 +2170,13 @@
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7026</v>
+        <v>-1.5497</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9408</v>
+        <v>-0.8397</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7618</v>
+        <v>-0.71</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4373</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-19.9319</v>
+        <v>-18.5835</v>
       </c>
       <c r="E23" t="n">
-        <v>2.575999999999998</v>
+        <v>2.576100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-22.5079</v>
+        <v>-21.1597</v>
       </c>
       <c r="G23" t="n">
         <v>-8.208600000000001</v>
@@ -2224,7 +2224,7 @@
         <v>19.7347</v>
       </c>
       <c r="K23" t="n">
-        <v>2.866299999999999</v>
+        <v>2.8663</v>
       </c>
       <c r="L23" t="n">
         <v>16.8684</v>
@@ -2248,13 +2248,13 @@
         <v>14.6507</v>
       </c>
       <c r="S23" t="n">
-        <v>-11.3491</v>
+        <v>-10.001</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.5702</v>
+        <v>-5.570099999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.7789</v>
+        <v>-4.4307</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3275</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484275_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484275_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,31 +570,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7672</v>
+        <v>5.8532</v>
       </c>
       <c r="E2" t="n">
-        <v>7.349</v>
+        <v>6.4351</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5819</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9489</v>
+        <v>3.0349</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5091</v>
+        <v>0.2021</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4398</v>
+        <v>2.8328</v>
       </c>
       <c r="J2" t="n">
-        <v>7.2159</v>
+        <v>6.3019</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6168</v>
+        <v>1.3098</v>
       </c>
       <c r="L2" t="n">
-        <v>5.5991</v>
+        <v>4.9921</v>
       </c>
       <c r="M2" t="n">
         <v>-3.267</v>
@@ -626,12 +631,17 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,28 +653,28 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9235</v>
+        <v>5.6165</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7921</v>
+        <v>3.4851</v>
       </c>
       <c r="F3" t="n">
         <v>2.1314</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5795</v>
+        <v>4.2725</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0136</v>
+        <v>3.7066</v>
       </c>
       <c r="I3" t="n">
         <v>0.5659</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0504</v>
+        <v>3.7434</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8885</v>
+        <v>3.5815</v>
       </c>
       <c r="L3" t="n">
         <v>0.1619</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8595</v>
+        <v>0.914</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7874</v>
+        <v>0.914</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9278999999999999</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3888</v>
+        <v>0.914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.241</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1478</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9619</v>
+        <v>0.914</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2507</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7112</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5731</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0097</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5634</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3303</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4664</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8638</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6353</v>
+        <v>0.8595</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1727</v>
+        <v>1.7874</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5374</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8303</v>
+        <v>0.3888</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0297</v>
+        <v>0.241</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.86</v>
+        <v>0.1478</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1707</v>
+        <v>2.9619</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9279</v>
+        <v>0.2507</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2428</v>
+        <v>2.7112</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.001</v>
+        <v>-2.5731</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8982</v>
+        <v>-0.0097</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.1028</v>
+        <v>-2.5634</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0051</v>
+        <v>1.3303</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7135</v>
+        <v>0.4664</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2916</v>
+        <v>0.8638</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4557</v>
+        <v>0.6353</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6191</v>
+        <v>3.1727</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1634</v>
+        <v>-2.5374</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8386</v>
+        <v>-0.8303</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1054</v>
+        <v>2.0297</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2669</v>
+        <v>-2.86</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8925999999999999</v>
+        <v>3.1707</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.4303</v>
+        <v>2.9279</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5377</v>
+        <v>0.2428</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0541</v>
+        <v>-4.001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3249</v>
+        <v>-0.8982</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2708</v>
+        <v>-3.1028</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2229</v>
+        <v>2.0051</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2037</v>
+        <v>1.7135</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0192</v>
+        <v>0.2916</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7445</v>
+        <v>0.307</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4491</v>
+        <v>0.307</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2955</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.283</v>
+        <v>0.307</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8017</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4812</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5336</v>
+        <v>0.307</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9414</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7494</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2095</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3198</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0613</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2586</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1328,12 +1378,17 @@
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>20.5369</v>
+        <v>-1.4557</v>
       </c>
       <c r="E12" t="n">
-        <v>23.113</v>
+        <v>-3.6191</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5762</v>
+        <v>2.1634</v>
       </c>
       <c r="G12" t="n">
-        <v>8.208600000000002</v>
+        <v>-0.8386</v>
       </c>
       <c r="H12" t="n">
-        <v>9.5588</v>
+        <v>-2.1054</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.350100000000001</v>
+        <v>1.2669</v>
       </c>
       <c r="J12" t="n">
-        <v>27.9433</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>12.4252</v>
+        <v>-2.4303</v>
       </c>
       <c r="L12" t="n">
-        <v>15.5182</v>
+        <v>1.5377</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.7347</v>
+        <v>0.0541</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.8663</v>
+        <v>0.3249</v>
       </c>
       <c r="O12" t="n">
-        <v>-16.8682</v>
+        <v>-0.2708</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9534</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.6505</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6974</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>11.9544</v>
+        <v>1.2229</v>
       </c>
       <c r="T12" t="n">
-        <v>6.384099999999999</v>
+        <v>0.2037</v>
       </c>
       <c r="U12" t="n">
-        <v>5.570200000000001</v>
+        <v>1.0192</v>
       </c>
       <c r="V12" t="n">
-        <v>2.327399999999999</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>3.4363</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1088</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5307</v>
+        <v>-3.7445</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4753</v>
+        <v>-3.4491</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9446</v>
+        <v>-0.2955</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9283</v>
+        <v>-3.283</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3671</v>
+        <v>-0.8017</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5612</v>
+        <v>-2.4812</v>
       </c>
       <c r="J13" t="n">
-        <v>6.7999</v>
+        <v>-2.5336</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6193</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>5.1806</v>
+        <v>-1.9414</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.8716</v>
+        <v>-0.7494</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2522</v>
+        <v>-0.2095</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6194</v>
+        <v>-0.5399</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.765</v>
+        <v>0.3198</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9339</v>
+        <v>0.0613</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.831</v>
+        <v>0.2586</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6133</v>
+        <v>20.5369</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0883</v>
+        <v>23.1131</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.475</v>
+        <v>-2.5762</v>
       </c>
       <c r="G14" t="n">
-        <v>8.462199999999999</v>
+        <v>8.208600000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3152</v>
+        <v>9.558800000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>8.147</v>
+        <v>-1.350100000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>12.0831</v>
+        <v>27.9433</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0466</v>
+        <v>12.4252</v>
       </c>
       <c r="L14" t="n">
-        <v>10.0365</v>
+        <v>15.5182</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.6208</v>
+        <v>-19.7347</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7314</v>
+        <v>-2.8663</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8895</v>
+        <v>-16.8682</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5627</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.9069</v>
+        <v>-14.6505</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3441</v>
+        <v>12.6974</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0676</v>
+        <v>11.9544</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0879</v>
+        <v>6.384099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9796</v>
+        <v>5.570200000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2186</v>
+        <v>2.327399999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.4363</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-1.1088</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7338</v>
+        <v>4.5307</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7663</v>
+        <v>6.4753</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5001</v>
+        <v>-1.9446</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0639</v>
+        <v>3.9283</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1179</v>
+        <v>0.3671</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0541</v>
+        <v>3.5612</v>
       </c>
       <c r="J15" t="n">
-        <v>1.904</v>
+        <v>6.7999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6357</v>
+        <v>1.6193</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2683</v>
+        <v>5.1806</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9678</v>
+        <v>-2.8716</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7536</v>
+        <v>-1.2522</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2142</v>
+        <v>-1.6194</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2792</v>
+        <v>-1.765</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1609</v>
+        <v>-0.9339</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1183</v>
+        <v>-0.831</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2768</v>
+        <v>2.0853</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6107</v>
+        <v>5.5603</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8875</v>
+        <v>-3.475</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9599</v>
+        <v>6.9343</v>
       </c>
       <c r="H16" t="n">
-        <v>0.077</v>
+        <v>-0.6058</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0369</v>
+        <v>7.54</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7571</v>
+        <v>10.5551</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3098</v>
+        <v>1.1256</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5527</v>
+        <v>9.429500000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.717</v>
+        <v>-3.6208</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2328</v>
+        <v>-1.7314</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4842</v>
+        <v>-1.8895</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.489</v>
+        <v>-2.0676</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1464</v>
+        <v>-1.0879</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3426</v>
+        <v>-0.9796</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8697</v>
+        <v>1.5279</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3546</v>
+        <v>1.5279</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5151</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6254</v>
+        <v>1.5279</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8836000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7418</v>
+        <v>0.607</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0313</v>
+        <v>1.5279</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2891</v>
+        <v>0.921</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7422</v>
+        <v>0.607</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6567</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1727</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.484</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4945</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4092</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0854</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1266</v>
+        <v>0.914</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3007</v>
+        <v>0.914</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4273</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6493</v>
+        <v>0.914</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9355</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7138</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9519</v>
+        <v>0.914</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1023</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8496</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.6012</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5634</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5675</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6512</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0838</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0258</v>
+        <v>-0.7338</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7265</v>
+        <v>0.7663</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2993</v>
+        <v>-1.5001</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6625</v>
+        <v>-0.0639</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0573</v>
+        <v>-0.1179</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6052</v>
+        <v>0.0541</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6751</v>
+        <v>1.904</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6102</v>
+        <v>0.6357</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0649</v>
+        <v>1.2683</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9874</v>
+        <v>-1.9678</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4472</v>
+        <v>-0.7536</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5403</v>
+        <v>-1.2142</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2498</v>
+        <v>-0.2792</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5976</v>
+        <v>-0.1609</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6522</v>
+        <v>-0.1183</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.2952</v>
+        <v>-1.2768</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7893</v>
+        <v>0.6107</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.506</v>
+        <v>-1.8875</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5557</v>
+        <v>-1.9599</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0967</v>
+        <v>0.077</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4589</v>
+        <v>-2.0369</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5666</v>
+        <v>0.7571</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3505</v>
+        <v>1.3098</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2161</v>
+        <v>-0.5527</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1223</v>
+        <v>-2.717</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4472</v>
+        <v>-1.2328</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6751</v>
+        <v>-1.4842</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7862</v>
+        <v>-0.489</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.449</v>
+        <v>-0.1464</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3372</v>
+        <v>-0.3426</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5475</v>
+        <v>-1.8697</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2638</v>
+        <v>-0.3546</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2837</v>
+        <v>-1.5151</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.4359</v>
+        <v>-1.6254</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.9786</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4574</v>
+        <v>-0.7418</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9695</v>
+        <v>1.0313</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.9407</v>
+        <v>0.2891</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9712</v>
+        <v>0.7422</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4664</v>
+        <v>-2.6567</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0379</v>
+        <v>-1.1727</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4285</v>
+        <v>-1.484</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.4945</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2943</v>
+        <v>-0.4092</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4582</v>
+        <v>-0.0854</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6642</v>
+        <v>0.0549</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.8521</v>
+        <v>-2.1266</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.531</v>
+        <v>1.3007</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3211</v>
+        <v>-3.4273</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.6465</v>
+        <v>-1.6493</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2484</v>
+        <v>-0.9355</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3981</v>
+        <v>-0.7138</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7146</v>
+        <v>1.9519</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0639</v>
+        <v>0.1023</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7785</v>
+        <v>1.8496</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.932</v>
+        <v>-3.6012</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3123</v>
+        <v>-1.0379</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6196</v>
+        <v>-2.5634</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5497</v>
+        <v>-0.5675</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8397</v>
+        <v>-0.6512</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.71</v>
+        <v>0.0838</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4373</v>
+        <v>-0.8865</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,401 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.5835</v>
+        <v>-4.0258</v>
       </c>
       <c r="E23" t="n">
-        <v>2.576100000000001</v>
+        <v>-3.7265</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.2993</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3.6625</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.0573</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.6052</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.6751</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.6102</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.0649</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.9874</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.4472</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.5403</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.2498</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.5976</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.6522</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>O. TOURE JABBY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.2952</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.7893</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.506</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.5557</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.0967</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.4589</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5666</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2161</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.1223</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.4472</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.6751</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.7862</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.449</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.3372</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M. TORNE DELAURENS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-5.4615</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.1778</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.2837</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-6.3499</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-4.2856</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.0643</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.8835</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-3.2477</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.4664</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.0379</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-2.4285</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.7524999999999999</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2943</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.4582</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J. JUAREZ GIMENEZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-7.8521</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.531</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-4.3211</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.6465</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.2484</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-3.3981</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.7146</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.7785</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.932</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.3123</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.6196</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1.5497</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.8397</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484275_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-18.5836</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.576000000000001</v>
+      </c>
+      <c r="F27" t="n">
         <v>-21.1597</v>
       </c>
-      <c r="G23" t="n">
-        <v>-8.208600000000001</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-9.558700000000002</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.350200000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>19.7347</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="G27" t="n">
+        <v>-8.208599999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-9.5587</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.350300000000002</v>
+      </c>
+      <c r="J27" t="n">
+        <v>19.7346</v>
+      </c>
+      <c r="K27" t="n">
         <v>2.8663</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L27" t="n">
         <v>16.8684</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M27" t="n">
         <v>-27.9432</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N27" t="n">
         <v>-12.4252</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O27" t="n">
         <v>-15.5182</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P27" t="n">
         <v>1.9535</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q27" t="n">
         <v>-12.6973</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R27" t="n">
         <v>14.6507</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S27" t="n">
         <v>-10.001</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T27" t="n">
         <v>-5.570099999999999</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U27" t="n">
         <v>-4.4307</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V27" t="n">
         <v>-2.3275</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W27" t="n">
         <v>1.1089</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X27" t="n">
         <v>-3.4364</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
